--- a/data/preliminaries/stellar/female/21-preliminary-r06-stellar-female.xlsx
+++ b/data/preliminaries/stellar/female/21-preliminary-r06-stellar-female.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
